--- a/每日输出/高短/郑州-高短-销售风灵在线率明细数据.xlsx
+++ b/每日输出/高短/郑州-高短-销售风灵在线率明细数据.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,8 +36,11 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -59,8 +62,13 @@
         <fgColor rgb="00F79646"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCE6F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="8">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -82,77 +90,11 @@
         <color rgb="00000000"/>
       </bottom>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="00000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="00000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="00000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="00000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="00000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -163,8 +105,18 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -530,13 +482,940 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:X9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>无数据</t>
+          <t>服务期</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>运营中心</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>分部</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>系统来源</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>学段</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>wehook_id</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>阶段</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>战队</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>学习规划师姓名</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>学习规划师邮箱</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>推广产品</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>风灵在线率</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>不在线时段list</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>app在线率</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>app不在线时段list</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>pc在线率</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>pc不在线时段list</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>年级</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>老师姓名</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>销售邮箱</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>sys_source</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>学部</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>分组</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>20261009</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>郑州一部</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>高阶</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1688856542873658</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>高阶一</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>纵马扬锋-陈春雨</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>秦盈盈</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>qinyingying</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>高一</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>秦盈盈</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>qinyingying</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>20261009</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>郑州一部</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>高阶</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1688856890900501</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>高阶一</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>纵马扬锋-陈春雨</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>陈春雨</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>chenchunyu</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>12,14,23</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>高一</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>陈春雨</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>chenchunyu</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>20261009</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>郑州一部</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>高阶</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1688854336892123</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>高阶一</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>纵马扬锋-陈春雨</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>刘培豪</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>liupeihao</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>10,11,12,13</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>高一</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>刘培豪</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>liupeihao</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>20261009</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>郑州一部</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>高阶</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1688855440766504</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>高阶一</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>纵马扬锋-陈春雨</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>邢若湘</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>xingruoxiang</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>高一</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>邢若湘</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>xingruoxiang</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>20261009</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>郑州一部</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>高阶</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1688856470815243</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>高阶一</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>纵马扬锋-陈春雨</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>李琳</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>lilin01</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>高一</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>李琳</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>lilin01</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>20261009</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>郑州一部</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>高阶</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1688856077781007</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>高阶一</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>纵马扬锋-陈春雨</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>李欣怡</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>lixinyi</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>高一</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>李欣怡</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>lixinyi</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>20261009</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>郑州一部</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>高阶</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1688856736832386,1688857349903222</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>高阶一</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>纵马扬锋-陈春雨</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>胡利晓</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>hulixiao</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>高一</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>胡利晓</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>hulixiao</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>20261009</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>郑州一部</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>高阶</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1688855111787697</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>高阶一</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>纵马扬锋-陈春雨</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>曹文浩</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>caowenhao</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>高一</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>曹文浩</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>caowenhao</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>高短</t>
         </is>
       </c>
     </row>
@@ -551,14 +1430,137 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>无数据</t>
-        </is>
+          <t>学部</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>年级</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>战队</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>接流人数</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>电脑端全天在线人数</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>电脑端全天在线率</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>手机端全天在线人数</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>手机端全天在线率</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>高一</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>纵马扬锋-陈春雨</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>高一 汇总</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>高短 汇总</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.75</v>
       </c>
     </row>
   </sheetData>
@@ -572,7 +1574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -588,7 +1590,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>企微风灵全天在线情况通晒（高短）-9月20日</t>
+          <t>企微风灵全天在线情况通晒（高短）-10月7日</t>
         </is>
       </c>
     </row>
@@ -618,19 +1620,19 @@
           <t>电脑端全天在线情况</t>
         </is>
       </c>
-      <c r="F2" s="4" t="n"/>
+      <c r="F2" s="2" t="n"/>
       <c r="G2" s="3" t="inlineStr">
         <is>
           <t>手机端全天在线情况</t>
         </is>
       </c>
-      <c r="H2" s="4" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n"/>
-      <c r="B3" s="5" t="n"/>
-      <c r="C3" s="5" t="n"/>
-      <c r="D3" s="5" t="n"/>
+      <c r="A3" s="2" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="inlineStr">
         <is>
           <t>人数</t>
@@ -650,17 +1652,105 @@
         <is>
           <t>全天在线率</t>
         </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>高一</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>纵马扬锋-陈春雨</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>高一 汇总</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr"/>
+      <c r="D5" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="H5" s="7" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>高短</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>高短 汇总</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr"/>
+      <c r="D6" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>0.75</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A2:A3"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="C2:C3"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
